--- a/output/2026-09-20_22_Croazia_Istarska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-20_22_Croazia_Istarska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore/rivenditore di utensili professionali, rappresentante Makita, Metabo, Bosch Professional, Flex, Ridgid, Rems, Beta, Proxxon, Karcher, Knipex, Rodcraft, Projahn. Confermato da sito ufficiale attivo con e-shop.</t>
+          <t>Distributore/rivenditore di utensili professionali, rappresentante Makita, Metabo, Bosch Professional, Flex, Ridgid, Rems, Beta, Proxxon, Karcher, Knipex, Rodcraft, Projahn. Confermato da sito ufficiale attivo con e-shop. [DUPLICATO — vedi anche: 2026-09-20_22_Croazia_Istarska_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,6 @@
           <t>OMAR d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Livade, Motovun (Istarska)</t>
@@ -658,7 +657,6 @@
           <t>052/664072</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Vendita e affilatura di utensili da taglio manuali. Piccola azienda locale (referente Boris Pogorevac), confermata via directory tvrtke.hr. Nessun sito web/email reperiti.</t>
@@ -676,7 +674,6 @@
           <t>D. &amp; Š. Alati (obrt)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Labin / Potpićan (Istarska)</t>
@@ -714,7 +711,6 @@
           <t>HR Metaloprema d.o.o.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Buzet (Istarska)</t>
@@ -752,7 +748,6 @@
           <t>Ravucommerce d.o.o.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Umag (Istarska)</t>
@@ -768,7 +763,6 @@
           <t>052/751460</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Ferramenta generalista (zeljezarija) - vendita al dettaglio di ferramenta, vernici, materiali edili, con utensili manuali/elettrici tra i prodotti. Fondata 1993. Confermata su fininfo, tvrtke.hr, Kompass.</t>
@@ -786,7 +780,6 @@
           <t>Zeljezarija Ferro (obrt, vl. Sanja Vareško)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Pula (Istarska)</t>
@@ -802,7 +795,6 @@
           <t>052 540 061 / 052 939 777</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Ditta individuale (obrt) attiva dal 1991, confermata su fininfo/infobiz e directory locali. Vende utensili e macchine utensili, utensili da giardino/elettrici/da costruzione, utensili da taglio e molatura, materiali di fissaggio.</t>

--- a/output/2026-09-20_22_Croazia_Istarska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-20_22_Croazia_Istarska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
